--- a/references/Mapping_FCT_LOAN_template .xlsx
+++ b/references/Mapping_FCT_LOAN_template .xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C20EB79-1E23-1248-A41D-2535C24549EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842B8FF3-69E8-024C-BFCA-8B799C8FF097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16880" tabRatio="365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mapping" sheetId="1" r:id="rId1"/>
@@ -3126,34 +3126,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3174,140 +3150,138 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3626,2886 +3600,2880 @@
   <dimension ref="A1:F2480"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19" style="3" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="59.1640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.1640625" style="3"/>
+    <col min="1" max="1" width="34.33203125" style="19" customWidth="1"/>
+    <col min="2" max="2" width="19" style="19" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.5" style="19" customWidth="1"/>
+    <col min="6" max="6" width="59.1640625" style="16" customWidth="1"/>
+    <col min="7" max="16384" width="9.1640625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="18" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="18" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="18" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="18" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="27"/>
-      <c r="E5" s="30" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="E5" s="18" t="s">
         <v>495</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="18" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="27"/>
-      <c r="E6" s="30" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="13"/>
+      <c r="E6" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="18" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="E7" s="30" t="s">
+      <c r="A7" s="13"/>
+      <c r="E7" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="23" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="E8" s="30" t="s">
+      <c r="A8" s="13"/>
+      <c r="E8" s="22" t="s">
         <v>371</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="24" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="E9" s="34" t="s">
+      <c r="A9" s="13"/>
+      <c r="E9" s="24" t="s">
         <v>356</v>
       </c>
-      <c r="F9" s="30"/>
+      <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="E10" s="34" t="s">
+      <c r="A10" s="13"/>
+      <c r="E10" s="24" t="s">
         <v>384</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="22" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="E11" s="34" t="s">
+      <c r="A11" s="13"/>
+      <c r="E11" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="22" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="30"/>
+      <c r="A12" s="13"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="22"/>
     </row>
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="E13" s="34" t="s">
+      <c r="A13" s="13"/>
+      <c r="E13" s="24" t="s">
         <v>489</v>
       </c>
-      <c r="F13" s="30"/>
+      <c r="F13" s="22"/>
     </row>
     <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
+      <c r="A14" s="13"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="66" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="9" t="s">
         <v>535</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="64" t="s">
+      <c r="E16" s="6"/>
+      <c r="F16" s="12" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21" t="s">
+      <c r="D17" s="28"/>
+      <c r="E17" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="29" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="8" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="35"/>
-      <c r="E19" s="22" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="8" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+    <row r="20" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="23" t="s">
+      <c r="D20" s="29"/>
+      <c r="E20" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="31" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="16" t="s">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="8" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="16" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="16" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="5" t="s">
+      <c r="D27" s="32"/>
+      <c r="E27" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="8" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="29" t="s">
         <v>225</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="5" t="s">
+      <c r="D33" s="33"/>
+      <c r="E33" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="16" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="8" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5" t="s">
+      <c r="D35" s="8"/>
+      <c r="E35" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5" t="s">
+      <c r="D36" s="8"/>
+      <c r="E36" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5" t="s">
+      <c r="D37" s="8"/>
+      <c r="E37" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="F37" s="8" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5" t="s">
+      <c r="D38" s="8"/>
+      <c r="E38" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="8" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F39" s="16" t="s">
+      <c r="D39" s="8"/>
+      <c r="E39" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F40" s="16" t="s">
+      <c r="D40" s="8"/>
+      <c r="E40" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F41" s="16" t="s">
+      <c r="D41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="34" t="s">
         <v>210</v>
       </c>
       <c r="C42" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5" t="s">
+      <c r="D42" s="8"/>
+      <c r="E42" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="F42" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="25"/>
-      <c r="E43" s="18" t="s">
+      <c r="D43" s="33"/>
+      <c r="E43" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="25"/>
-      <c r="E44" s="9" t="s">
+      <c r="D44" s="33"/>
+      <c r="E44" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35" t="s">
+      <c r="D45" s="8"/>
+      <c r="E45" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="8" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="39"/>
-      <c r="E46" s="35" t="s">
+      <c r="D46" s="27"/>
+      <c r="E46" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="F46" s="35" t="s">
+      <c r="F46" s="8" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="F47" s="35" t="s">
+      <c r="D47" s="27"/>
+      <c r="E47" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="F48" s="35"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="F49" s="35" t="s">
+      <c r="D49" s="27"/>
+      <c r="E49" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F49" s="8" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="25"/>
-      <c r="E50" s="6" t="s">
+      <c r="D50" s="33"/>
+      <c r="E50" s="32" t="s">
         <v>519</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="32" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A51" s="37" t="s">
+      <c r="A51" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D51" s="25"/>
-      <c r="E51" s="6" t="s">
+      <c r="D51" s="33"/>
+      <c r="E51" s="32" t="s">
         <v>520</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="32" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A52" s="37" t="s">
+      <c r="A52" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="25"/>
-      <c r="E52" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="D52" s="33"/>
+      <c r="E52" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F52" s="32" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A53" s="37" t="s">
+      <c r="A53" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D53" s="25"/>
-      <c r="E53" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F53" s="6" t="s">
+      <c r="D53" s="33"/>
+      <c r="E53" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F53" s="32" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A54" s="37" t="s">
+      <c r="A54" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="D54" s="25"/>
-      <c r="E54" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F54" s="6" t="s">
+      <c r="D54" s="33"/>
+      <c r="E54" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F54" s="32" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A55" s="37" t="s">
+      <c r="A55" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="D55" s="25"/>
-      <c r="E55" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" s="6" t="s">
+      <c r="D55" s="33"/>
+      <c r="E55" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="F55" s="32" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A56" s="38" t="s">
+      <c r="A56" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D56" s="41" t="s">
+      <c r="D56" s="35" t="s">
         <v>494</v>
       </c>
-      <c r="E56" s="21" t="s">
+      <c r="E56" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A57" s="38" t="s">
+      <c r="A57" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="E57" s="9" t="s">
+      <c r="E57" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A58" s="38" t="s">
+      <c r="A58" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="35"/>
-      <c r="E58" s="9" t="s">
+      <c r="D58" s="8"/>
+      <c r="E58" s="26" t="s">
         <v>441</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="38" t="s">
+      <c r="A59" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="D59" s="35"/>
-      <c r="E59" s="9" t="s">
+      <c r="D59" s="8"/>
+      <c r="E59" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A60" s="38" t="s">
+      <c r="A60" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="27" t="s">
         <v>471</v>
       </c>
-      <c r="D60" s="35"/>
-      <c r="E60" s="9" t="s">
+      <c r="D60" s="8"/>
+      <c r="E60" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="38" t="s">
+      <c r="A61" s="29" t="s">
         <v>491</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="27" t="s">
         <v>492</v>
       </c>
-      <c r="D61" s="35"/>
-      <c r="E61" s="9" t="s">
+      <c r="D61" s="8"/>
+      <c r="E61" s="26" t="s">
         <v>493</v>
       </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="8"/>
     </row>
     <row r="62" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A62" s="37" t="s">
+      <c r="A62" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="36"/>
-      <c r="E62" s="5" t="s">
+      <c r="D62" s="33"/>
+      <c r="E62" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A63" s="37" t="s">
+      <c r="A63" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="B63" s="40" t="s">
+      <c r="B63" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C63" s="39" t="s">
+      <c r="C63" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D63" s="36"/>
-      <c r="E63" s="35" t="s">
+      <c r="D63" s="33"/>
+      <c r="E63" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="F63" s="35"/>
+      <c r="F63" s="8"/>
     </row>
     <row r="64" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A64" s="38" t="s">
+      <c r="A64" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="B64" s="40" t="s">
+      <c r="B64" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="C64" s="39" t="s">
+      <c r="C64" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="D64" s="39" t="s">
+      <c r="D64" s="27" t="s">
         <v>526</v>
       </c>
-      <c r="E64" s="35" t="s">
+      <c r="E64" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="F64" s="35" t="s">
+      <c r="F64" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="38" t="s">
+      <c r="A65" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B65" s="40" t="s">
+      <c r="B65" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C65" s="39" t="s">
+      <c r="C65" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="35"/>
-      <c r="E65" s="38" t="s">
+      <c r="D65" s="8"/>
+      <c r="E65" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="F65" s="35" t="s">
+      <c r="F65" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A66" s="35" t="s">
+      <c r="A66" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B66" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C66" s="35" t="s">
+      <c r="C66" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35" t="s">
+      <c r="D66" s="8"/>
+      <c r="E66" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="F66" s="35" t="s">
+      <c r="F66" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="40" t="s">
+      <c r="A67" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="B67" s="40" t="s">
+      <c r="B67" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C67" s="35" t="s">
+      <c r="C67" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35" t="s">
+      <c r="D67" s="8"/>
+      <c r="E67" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="B68" s="40" t="s">
+      <c r="B68" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C68" s="35" t="s">
+      <c r="C68" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35" t="s">
+      <c r="D68" s="8"/>
+      <c r="E68" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="F68" s="35" t="s">
+      <c r="F68" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A69" s="40" t="s">
+      <c r="A69" s="26" t="s">
         <v>335</v>
       </c>
-      <c r="B69" s="40" t="s">
+      <c r="B69" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C69" s="35" t="s">
+      <c r="C69" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35" t="s">
+      <c r="D69" s="8"/>
+      <c r="E69" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="F69" s="35" t="s">
+      <c r="F69" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="40" t="s">
+      <c r="B70" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C70" s="35" t="s">
+      <c r="C70" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35" t="s">
+      <c r="D70" s="8"/>
+      <c r="E70" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="F70" s="35" t="s">
+      <c r="F70" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A71" s="40" t="s">
+      <c r="A71" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="B71" s="40" t="s">
+      <c r="B71" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C71" s="35" t="s">
+      <c r="C71" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="D71" s="35"/>
-      <c r="E71" s="35" t="s">
+      <c r="D71" s="8"/>
+      <c r="E71" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="F71" s="35" t="s">
+      <c r="F71" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A72" s="40" t="s">
+      <c r="A72" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="B72" s="40" t="s">
+      <c r="B72" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C72" s="35" t="s">
+      <c r="C72" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35" t="s">
+      <c r="D72" s="8"/>
+      <c r="E72" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="F72" s="35" t="s">
+      <c r="F72" s="8" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A73" s="35" t="s">
+      <c r="A73" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="B73" s="40" t="s">
+      <c r="B73" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C73" s="35" t="s">
+      <c r="C73" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35" t="s">
+      <c r="D73" s="8"/>
+      <c r="E73" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="F73" s="35" t="s">
+      <c r="F73" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A74" s="35" t="s">
+      <c r="A74" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="B74" s="40" t="s">
+      <c r="B74" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C74" s="35" t="s">
+      <c r="C74" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="D74" s="41"/>
-      <c r="E74" s="35" t="s">
+      <c r="D74" s="35"/>
+      <c r="E74" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="F74" s="35" t="s">
+      <c r="F74" s="8" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A75" s="40" t="s">
+      <c r="A75" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="B75" s="40" t="s">
+      <c r="B75" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C75" s="35" t="s">
+      <c r="C75" s="8" t="s">
         <v>327</v>
       </c>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35" t="s">
+      <c r="D75" s="8"/>
+      <c r="E75" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="F75" s="35" t="s">
+      <c r="F75" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="B76" s="40" t="s">
+      <c r="B76" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C76" s="35" t="s">
+      <c r="C76" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35" t="s">
+      <c r="D76" s="8"/>
+      <c r="E76" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="F76" s="35" t="s">
+      <c r="F76" s="8" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A77" s="35" t="s">
+      <c r="A77" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B77" s="40" t="s">
+      <c r="B77" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C77" s="35" t="s">
+      <c r="C77" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35" t="s">
+      <c r="D77" s="8"/>
+      <c r="E77" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F77" s="35" t="s">
+      <c r="F77" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A78" s="35" t="s">
+      <c r="A78" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B78" s="40" t="s">
+      <c r="B78" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C78" s="35" t="s">
+      <c r="C78" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35" t="s">
+      <c r="D78" s="8"/>
+      <c r="E78" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="F78" s="35" t="s">
+      <c r="F78" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B79" s="40" t="s">
+      <c r="B79" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C79" s="35" t="s">
+      <c r="C79" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="F79" s="35" t="s">
+      <c r="D79" s="8"/>
+      <c r="E79" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F79" s="8" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A80" s="35" t="s">
+      <c r="A80" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B80" s="40" t="s">
+      <c r="B80" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C80" s="35" t="s">
+      <c r="C80" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D80" s="35"/>
-      <c r="E80" s="35" t="s">
+      <c r="D80" s="8"/>
+      <c r="E80" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="F80" s="35" t="s">
+      <c r="F80" s="8" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A81" s="42" t="s">
+      <c r="A81" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B81" s="40"/>
-      <c r="C81" s="42" t="s">
+      <c r="B81" s="26"/>
+      <c r="C81" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="D81" s="35"/>
-      <c r="E81" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="F81" s="35" t="s">
+      <c r="D81" s="8"/>
+      <c r="E81" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A82" s="38" t="s">
+      <c r="A82" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="B82" s="40" t="s">
+      <c r="B82" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C82" s="39"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="35" t="s">
+      <c r="C82" s="27"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F82" s="35" t="s">
+      <c r="F82" s="8" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A83" s="43" t="s">
+      <c r="A83" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="B83" s="40" t="s">
+      <c r="B83" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C83" s="40" t="s">
+      <c r="C83" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="D83" s="35"/>
-      <c r="E83" s="35" t="s">
+      <c r="D83" s="8"/>
+      <c r="E83" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F83" s="44" t="s">
+      <c r="F83" s="37" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A84" s="38" t="s">
+      <c r="A84" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="B84" s="40" t="s">
+      <c r="B84" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C84" s="35" t="s">
+      <c r="C84" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D84" s="35"/>
-      <c r="E84" s="35" t="s">
+      <c r="D84" s="8"/>
+      <c r="E84" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F84" s="35" t="s">
+      <c r="F84" s="8" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="38" t="s">
+      <c r="A85" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="B85" s="40" t="s">
+      <c r="B85" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C85" s="35"/>
-      <c r="D85" s="35"/>
-      <c r="E85" s="35" t="s">
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="F85" s="35" t="s">
+      <c r="F85" s="8" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="38" t="s">
+      <c r="A86" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="B86" s="40" t="s">
+      <c r="B86" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C86" s="39"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35" t="s">
+      <c r="C86" s="27"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F86" s="35" t="s">
+      <c r="F86" s="8" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="38" t="s">
+      <c r="A87" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="B87" s="40" t="s">
+      <c r="B87" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="C87" s="35" t="s">
+      <c r="C87" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D87" s="35"/>
-      <c r="E87" s="44" t="s">
+      <c r="D87" s="8"/>
+      <c r="E87" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="F87" s="35" t="s">
+      <c r="F87" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A88" s="37" t="s">
+      <c r="A88" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="B88" s="40" t="s">
+      <c r="B88" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C88" s="39" t="s">
+      <c r="C88" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="D88" s="35"/>
-      <c r="E88" s="35" t="s">
+      <c r="D88" s="8"/>
+      <c r="E88" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F88" s="35" t="s">
+      <c r="F88" s="8" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A89" s="35" t="s">
+      <c r="A89" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B89" s="40" t="s">
+      <c r="B89" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C89" s="39"/>
-      <c r="D89" s="35"/>
-      <c r="E89" s="35" t="s">
+      <c r="C89" s="27"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="F89" s="35" t="s">
+      <c r="F89" s="8" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A90" s="38" t="s">
+      <c r="A90" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="B90" s="40" t="s">
+      <c r="B90" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C90" s="35" t="s">
+      <c r="C90" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D90" s="35"/>
-      <c r="E90" s="35" t="s">
+      <c r="D90" s="8"/>
+      <c r="E90" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F90" s="35" t="s">
+      <c r="F90" s="8" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="38" t="s">
+      <c r="A91" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="B91" s="40" t="s">
+      <c r="B91" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C91" s="35"/>
-      <c r="D91" s="35"/>
-      <c r="E91" s="35" t="s">
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F91" s="35" t="s">
+      <c r="F91" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A92" s="38" t="s">
+      <c r="A92" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="B92" s="40" t="s">
+      <c r="B92" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C92" s="40" t="s">
+      <c r="C92" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="D92" s="35"/>
-      <c r="E92" s="35" t="s">
+      <c r="D92" s="8"/>
+      <c r="E92" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="F92" s="35" t="s">
+      <c r="F92" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A93" s="38" t="s">
+      <c r="A93" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B93" s="40" t="s">
+      <c r="B93" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C93" s="40"/>
-      <c r="D93" s="35"/>
-      <c r="E93" s="35" t="s">
+      <c r="C93" s="26"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F93" s="35" t="s">
+      <c r="F93" s="8" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A94" s="38" t="s">
+      <c r="A94" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="B94" s="40" t="s">
+      <c r="B94" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C94" s="40" t="s">
+      <c r="C94" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="D94" s="35"/>
-      <c r="E94" s="35" t="s">
+      <c r="D94" s="8"/>
+      <c r="E94" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F94" s="35" t="s">
+      <c r="F94" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="38" t="s">
+      <c r="A95" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B95" s="40" t="s">
+      <c r="B95" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C95" s="40"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="35" t="s">
+      <c r="C95" s="26"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="F95" s="35" t="s">
+      <c r="F95" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="45" t="s">
+      <c r="A96" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="B96" s="46" t="s">
+      <c r="B96" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="C96" s="46" t="s">
+      <c r="C96" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="D96" s="39"/>
-      <c r="E96" s="39" t="s">
+      <c r="D96" s="27"/>
+      <c r="E96" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="F96" s="39" t="s">
+      <c r="F96" s="27" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A97" s="45" t="s">
+      <c r="A97" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="B97" s="46" t="s">
+      <c r="B97" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="47" t="s">
+      <c r="C97" s="27"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="F97" s="39" t="s">
+      <c r="F97" s="27" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="45" t="s">
+      <c r="A98" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="B98" s="46" t="s">
+      <c r="B98" s="36" t="s">
         <v>243</v>
       </c>
-      <c r="C98" s="39"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="46" t="s">
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="F98" s="39"/>
+      <c r="F98" s="27"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="45" t="s">
+      <c r="A99" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="B99" s="40" t="s">
+      <c r="B99" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C99" s="39"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="46" t="s">
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="36" t="s">
         <v>320</v>
       </c>
-      <c r="F99" s="39"/>
+      <c r="F99" s="27"/>
     </row>
     <row r="100" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A100" s="38" t="s">
+      <c r="A100" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="B100" s="40" t="s">
+      <c r="B100" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="39" t="s">
+      <c r="C100" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="D100" s="37"/>
-      <c r="E100" s="40" t="s">
+      <c r="D100" s="32"/>
+      <c r="E100" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="F100" s="35" t="s">
+      <c r="F100" s="8" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="38" t="s">
+      <c r="A101" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="B101" s="40" t="s">
+      <c r="B101" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C101" s="39"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="40" t="s">
+      <c r="C101" s="27"/>
+      <c r="D101" s="40"/>
+      <c r="E101" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="F101" s="35" t="s">
+      <c r="F101" s="8" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A102" s="38" t="s">
+      <c r="A102" s="29" t="s">
         <v>224</v>
       </c>
-      <c r="B102" s="40" t="s">
+      <c r="B102" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="C102" s="35"/>
-      <c r="D102" s="35"/>
-      <c r="E102" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="F102" s="35" t="s">
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F102" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="38" t="s">
+      <c r="A103" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="B103" s="38" t="s">
+      <c r="B103" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="C103" s="35"/>
-      <c r="D103" s="35"/>
-      <c r="E103" s="35" t="s">
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="F103" s="35" t="s">
+      <c r="F103" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A104" s="38" t="s">
+      <c r="A104" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="B104" s="38" t="s">
+      <c r="B104" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="C104" s="35"/>
-      <c r="D104" s="35"/>
-      <c r="E104" s="35" t="s">
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="F104" s="35" t="s">
+      <c r="F104" s="8" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="38" t="s">
+      <c r="A105" s="29" t="s">
         <v>240</v>
       </c>
-      <c r="B105" s="38" t="s">
+      <c r="B105" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="C105" s="35"/>
-      <c r="D105" s="35"/>
-      <c r="E105" s="35" t="s">
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="F105" s="35" t="s">
+      <c r="F105" s="8" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="38" t="s">
+      <c r="A106" s="29" t="s">
         <v>274</v>
       </c>
-      <c r="B106" s="38" t="s">
+      <c r="B106" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="C106" s="35"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="35" t="s">
+      <c r="C106" s="8"/>
+      <c r="D106" s="33"/>
+      <c r="E106" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="F106" s="35" t="s">
+      <c r="F106" s="8" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="38" t="s">
+      <c r="A107" s="29" t="s">
         <v>275</v>
       </c>
-      <c r="B107" s="38" t="s">
+      <c r="B107" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C107" s="35"/>
-      <c r="D107" s="36"/>
-      <c r="E107" s="35" t="s">
+      <c r="C107" s="8"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F107" s="35" t="s">
+      <c r="F107" s="8" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A108" s="38" t="s">
+      <c r="A108" s="29" t="s">
         <v>276</v>
       </c>
-      <c r="B108" s="38" t="s">
+      <c r="B108" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="C108" s="35"/>
-      <c r="D108" s="36"/>
-      <c r="E108" s="35" t="s">
+      <c r="C108" s="8"/>
+      <c r="D108" s="33"/>
+      <c r="E108" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="F108" s="35" t="s">
+      <c r="F108" s="8" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="38" t="s">
+      <c r="A109" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="B109" s="38" t="s">
+      <c r="B109" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="C109" s="38"/>
-      <c r="D109" s="36"/>
-      <c r="E109" s="35" t="s">
+      <c r="C109" s="29"/>
+      <c r="D109" s="33"/>
+      <c r="E109" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="F109" s="35" t="s">
+      <c r="F109" s="8" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A110" s="38" t="s">
+      <c r="A110" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="B110" s="38" t="s">
+      <c r="B110" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C110" s="38"/>
-      <c r="D110" s="36"/>
-      <c r="E110" s="35" t="s">
+      <c r="C110" s="29"/>
+      <c r="D110" s="33"/>
+      <c r="E110" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="F110" s="35" t="s">
+      <c r="F110" s="8" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A111" s="38" t="s">
+      <c r="A111" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="B111" s="38" t="s">
+      <c r="B111" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="C111" s="38" t="s">
+      <c r="C111" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="D111" s="36"/>
-      <c r="E111" s="35" t="s">
+      <c r="D111" s="33"/>
+      <c r="E111" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="F111" s="35" t="s">
+      <c r="F111" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="38" t="s">
+      <c r="A112" s="29" t="s">
         <v>241</v>
       </c>
-      <c r="B112" s="38" t="s">
+      <c r="B112" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="C112" s="38" t="s">
+      <c r="C112" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="D112" s="36"/>
-      <c r="E112" s="35" t="s">
+      <c r="D112" s="33"/>
+      <c r="E112" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="F112" s="35" t="s">
+      <c r="F112" s="8" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="38" t="s">
+      <c r="A113" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="B113" s="38" t="s">
+      <c r="B113" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="C113" s="37"/>
-      <c r="D113" s="37"/>
-      <c r="E113" s="37" t="s">
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="F113" s="37" t="s">
+      <c r="F113" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A114" s="38" t="s">
+      <c r="A114" s="29" t="s">
         <v>262</v>
       </c>
-      <c r="B114" s="38" t="s">
+      <c r="B114" s="29" t="s">
         <v>243</v>
       </c>
-      <c r="C114" s="37"/>
-      <c r="D114" s="37"/>
-      <c r="E114" s="42" t="s">
+      <c r="C114" s="32"/>
+      <c r="D114" s="32"/>
+      <c r="E114" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="F114" s="37" t="s">
+      <c r="F114" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A115" s="42" t="s">
+      <c r="A115" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="B115" s="38" t="s">
+      <c r="B115" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C115" s="39" t="s">
+      <c r="C115" s="27" t="s">
         <v>271</v>
       </c>
-      <c r="D115" s="37"/>
-      <c r="E115" s="46" t="s">
+      <c r="D115" s="32"/>
+      <c r="E115" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="F115" s="37" t="s">
+      <c r="F115" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="49" t="s">
+      <c r="A116" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="B116" s="40" t="s">
+      <c r="B116" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C116" s="39" t="s">
+      <c r="C116" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="D116" s="37"/>
-      <c r="E116" s="46" t="s">
+      <c r="D116" s="32"/>
+      <c r="E116" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="F116" s="37" t="s">
+      <c r="F116" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="49" t="s">
+      <c r="A117" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="B117" s="40" t="s">
+      <c r="B117" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C117" s="39" t="s">
+      <c r="C117" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="D117" s="37"/>
-      <c r="E117" s="46" t="s">
+      <c r="D117" s="32"/>
+      <c r="E117" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="F117" s="37" t="s">
+      <c r="F117" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A118" s="49" t="s">
+      <c r="A118" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="B118" s="40" t="s">
+      <c r="B118" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C118" s="39"/>
-      <c r="D118" s="37"/>
-      <c r="E118" s="46" t="s">
+      <c r="C118" s="27"/>
+      <c r="D118" s="32"/>
+      <c r="E118" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="F118" s="37" t="s">
+      <c r="F118" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A119" s="49" t="s">
+      <c r="A119" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="B119" s="40" t="s">
+      <c r="B119" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C119" s="39"/>
-      <c r="D119" s="37"/>
-      <c r="E119" s="46" t="s">
+      <c r="C119" s="27"/>
+      <c r="D119" s="32"/>
+      <c r="E119" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="F119" s="37" t="s">
+      <c r="F119" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A120" s="49" t="s">
+      <c r="A120" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="B120" s="40" t="s">
+      <c r="B120" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C120" s="39" t="s">
+      <c r="C120" s="27" t="s">
         <v>283</v>
       </c>
-      <c r="D120" s="37"/>
-      <c r="E120" s="39" t="s">
+      <c r="D120" s="32"/>
+      <c r="E120" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="F120" s="37" t="s">
+      <c r="F120" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A121" s="35" t="s">
+      <c r="A121" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="B121" s="35" t="s">
+      <c r="B121" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="C121" s="35" t="s">
+      <c r="C121" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="D121" s="37"/>
-      <c r="E121" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="F121" s="35" t="s">
+      <c r="D121" s="32"/>
+      <c r="E121" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="F121" s="8" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A122" s="40" t="s">
+      <c r="A122" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="B122" s="40" t="s">
+      <c r="B122" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C122" s="40" t="s">
+      <c r="C122" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="D122" s="37"/>
-      <c r="E122" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="F122" s="35" t="s">
+      <c r="D122" s="32"/>
+      <c r="E122" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="F122" s="8" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A123" s="40" t="s">
+      <c r="A123" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="B123" s="40" t="s">
+      <c r="B123" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C123" s="40" t="s">
+      <c r="C123" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="D123" s="37" t="s">
+      <c r="D123" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="E123" s="35" t="s">
+      <c r="E123" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="F123" s="35"/>
+      <c r="F123" s="8"/>
     </row>
     <row r="124" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A124" s="50" t="s">
+      <c r="A124" s="42" t="s">
         <v>340</v>
       </c>
-      <c r="B124" s="51" t="s">
+      <c r="B124" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="C124" s="40" t="s">
+      <c r="C124" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="D124" s="50"/>
-      <c r="E124" s="39" t="s">
+      <c r="D124" s="42"/>
+      <c r="E124" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="F124" s="35" t="s">
+      <c r="F124" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A125" s="50" t="s">
+      <c r="A125" s="42" t="s">
         <v>341</v>
       </c>
-      <c r="B125" s="52" t="s">
+      <c r="B125" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C125" s="40"/>
-      <c r="D125" s="50"/>
-      <c r="E125" s="50" t="s">
+      <c r="C125" s="26"/>
+      <c r="D125" s="42"/>
+      <c r="E125" s="42" t="s">
         <v>344</v>
       </c>
-      <c r="F125" s="35" t="s">
+      <c r="F125" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" s="50" t="s">
+      <c r="A126" s="42" t="s">
         <v>374</v>
       </c>
-      <c r="B126" s="52" t="s">
+      <c r="B126" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C126" s="40"/>
-      <c r="D126" s="50"/>
-      <c r="E126" s="50" t="s">
+      <c r="C126" s="26"/>
+      <c r="D126" s="42"/>
+      <c r="E126" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="F126" s="35"/>
+      <c r="F126" s="8"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" s="50" t="s">
+      <c r="A127" s="42" t="s">
         <v>375</v>
       </c>
-      <c r="B127" s="52" t="s">
+      <c r="B127" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C127" s="40"/>
-      <c r="D127" s="50"/>
-      <c r="E127" s="50" t="s">
+      <c r="C127" s="26"/>
+      <c r="D127" s="42"/>
+      <c r="E127" s="42" t="s">
         <v>380</v>
       </c>
-      <c r="F127" s="35"/>
+      <c r="F127" s="8"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="50" t="s">
+      <c r="A128" s="42" t="s">
         <v>376</v>
       </c>
-      <c r="B128" s="52" t="s">
+      <c r="B128" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C128" s="40" t="s">
+      <c r="C128" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="D128" s="50"/>
-      <c r="E128" s="50" t="s">
+      <c r="D128" s="42"/>
+      <c r="E128" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="F128" s="35"/>
+      <c r="F128" s="8"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" s="50" t="s">
+      <c r="A129" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="B129" s="52" t="s">
+      <c r="B129" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C129" s="40"/>
-      <c r="D129" s="50"/>
-      <c r="E129" s="50" t="s">
+      <c r="C129" s="26"/>
+      <c r="D129" s="42"/>
+      <c r="E129" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="F129" s="35"/>
+      <c r="F129" s="8"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="50" t="s">
+      <c r="A130" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="B130" s="52" t="s">
+      <c r="B130" s="44" t="s">
         <v>171</v>
       </c>
-      <c r="C130" s="40"/>
-      <c r="D130" s="50"/>
-      <c r="E130" s="50" t="s">
+      <c r="C130" s="26"/>
+      <c r="D130" s="42"/>
+      <c r="E130" s="42" t="s">
         <v>382</v>
       </c>
-      <c r="F130" s="35"/>
+      <c r="F130" s="8"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" s="53" t="s">
+      <c r="A131" s="45" t="s">
         <v>387</v>
       </c>
-      <c r="B131" s="53" t="s">
+      <c r="B131" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="C131" s="53" t="s">
+      <c r="C131" s="45" t="s">
         <v>389</v>
       </c>
-      <c r="D131" s="51" t="s">
+      <c r="D131" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="E131" s="53" t="s">
+      <c r="E131" s="45" t="s">
         <v>391</v>
       </c>
-      <c r="F131" s="53"/>
+      <c r="F131" s="45"/>
     </row>
     <row r="132" spans="1:6" ht="60" x14ac:dyDescent="0.2">
-      <c r="A132" s="55" t="s">
+      <c r="A132" s="46" t="s">
         <v>386</v>
       </c>
-      <c r="B132" s="53" t="s">
+      <c r="B132" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="C132" s="53" t="s">
+      <c r="C132" s="45" t="s">
         <v>390</v>
       </c>
-      <c r="D132" s="51" t="s">
+      <c r="D132" s="43" t="s">
         <v>388</v>
       </c>
-      <c r="E132" s="53" t="s">
+      <c r="E132" s="45" t="s">
         <v>413</v>
       </c>
-      <c r="F132" s="53"/>
+      <c r="F132" s="45"/>
     </row>
     <row r="133" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A133" s="50" t="s">
+      <c r="A133" s="42" t="s">
         <v>392</v>
       </c>
-      <c r="B133" s="53" t="s">
+      <c r="B133" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C133" s="35" t="s">
+      <c r="C133" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="D133" s="51" t="s">
+      <c r="D133" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="E133" s="50" t="s">
+      <c r="E133" s="42" t="s">
         <v>398</v>
       </c>
-      <c r="F133" s="35" t="s">
+      <c r="F133" s="8" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A134" s="50" t="s">
+      <c r="A134" s="42" t="s">
         <v>429</v>
       </c>
-      <c r="B134" s="53" t="s">
+      <c r="B134" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="C134" s="35"/>
-      <c r="D134" s="51" t="s">
+      <c r="C134" s="8"/>
+      <c r="D134" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="E134" s="35" t="s">
+      <c r="E134" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="F134" s="35"/>
+      <c r="F134" s="8"/>
     </row>
     <row r="135" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="50" t="s">
+      <c r="A135" s="42" t="s">
         <v>393</v>
       </c>
-      <c r="B135" s="53" t="s">
+      <c r="B135" s="45" t="s">
         <v>396</v>
       </c>
-      <c r="C135" s="35" t="s">
+      <c r="C135" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="D135" s="51" t="s">
+      <c r="D135" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="E135" s="50" t="s">
+      <c r="E135" s="42" t="s">
         <v>402</v>
       </c>
-      <c r="F135" s="35" t="s">
+      <c r="F135" s="8" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A136" s="50" t="s">
+      <c r="A136" s="42" t="s">
         <v>394</v>
       </c>
-      <c r="B136" s="53" t="s">
+      <c r="B136" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C136" s="35" t="s">
+      <c r="C136" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="D136" s="51" t="s">
+      <c r="D136" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="E136" s="50" t="s">
+      <c r="E136" s="42" t="s">
         <v>405</v>
       </c>
-      <c r="F136" s="35" t="s">
+      <c r="F136" s="8" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A137" s="50" t="s">
+      <c r="A137" s="42" t="s">
         <v>395</v>
       </c>
-      <c r="B137" s="53" t="s">
+      <c r="B137" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C137" s="35" t="s">
+      <c r="C137" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="D137" s="51" t="s">
+      <c r="D137" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="E137" s="50" t="s">
+      <c r="E137" s="42" t="s">
         <v>408</v>
       </c>
-      <c r="F137" s="35" t="s">
+      <c r="F137" s="8" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="45" x14ac:dyDescent="0.2">
-      <c r="A138" s="56" t="s">
+      <c r="A138" s="47" t="s">
         <v>410</v>
       </c>
-      <c r="B138" s="51" t="s">
+      <c r="B138" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="C138" s="35" t="s">
+      <c r="C138" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="D138" s="51" t="s">
+      <c r="D138" s="43" t="s">
         <v>401</v>
       </c>
-      <c r="E138" s="57" t="s">
+      <c r="E138" s="48" t="s">
         <v>412</v>
       </c>
-      <c r="F138" s="57"/>
+      <c r="F138" s="48"/>
     </row>
     <row r="139" spans="1:6" ht="120" x14ac:dyDescent="0.2">
-      <c r="A139" s="51" t="s">
+      <c r="A139" s="43" t="s">
         <v>416</v>
       </c>
-      <c r="B139" s="53" t="s">
+      <c r="B139" s="45" t="s">
         <v>418</v>
       </c>
-      <c r="C139" s="35" t="s">
+      <c r="C139" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="D139" s="51" t="s">
+      <c r="D139" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="E139" s="57" t="s">
+      <c r="E139" s="48" t="s">
         <v>424</v>
       </c>
-      <c r="F139" s="57" t="s">
+      <c r="F139" s="48" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A140" s="58" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="43" t="s">
         <v>417</v>
       </c>
-      <c r="B140" s="40" t="s">
+      <c r="B140" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C140" s="35"/>
-      <c r="D140" s="51" t="s">
+      <c r="C140" s="8"/>
+      <c r="D140" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="E140" s="50" t="s">
+      <c r="E140" s="42" t="s">
         <v>422</v>
       </c>
-      <c r="F140" s="50" t="s">
+      <c r="F140" s="42" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="384" x14ac:dyDescent="0.2">
-      <c r="A141" s="51" t="s">
+      <c r="A141" s="43" t="s">
         <v>414</v>
       </c>
-      <c r="B141" s="53" t="s">
+      <c r="B141" s="45" t="s">
         <v>418</v>
       </c>
-      <c r="C141" s="35" t="s">
+      <c r="C141" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="D141" s="51" t="s">
+      <c r="D141" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="E141" s="57" t="s">
+      <c r="E141" s="48" t="s">
         <v>423</v>
       </c>
-      <c r="F141" s="57" t="s">
+      <c r="F141" s="48" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A142" s="58" t="s">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="43" t="s">
         <v>415</v>
       </c>
-      <c r="B142" s="40" t="s">
+      <c r="B142" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C142" s="35"/>
-      <c r="D142" s="51" t="s">
+      <c r="C142" s="8"/>
+      <c r="D142" s="43" t="s">
         <v>421</v>
       </c>
-      <c r="E142" s="50" t="s">
+      <c r="E142" s="42" t="s">
         <v>422</v>
       </c>
-      <c r="F142" s="50" t="s">
+      <c r="F142" s="42" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="34" x14ac:dyDescent="0.15">
-      <c r="A143" s="58" t="s">
+    <row r="143" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A143" s="43" t="s">
         <v>430</v>
       </c>
-      <c r="B143" s="59" t="s">
+      <c r="B143" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="C143" s="35" t="s">
+      <c r="C143" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="D143" s="51" t="s">
+      <c r="D143" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="E143" s="50" t="s">
+      <c r="E143" s="42" t="s">
         <v>433</v>
       </c>
-      <c r="F143" s="50" t="s">
+      <c r="F143" s="42" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A144" s="58" t="s">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="43" t="s">
         <v>435</v>
       </c>
-      <c r="B144" s="59" t="s">
+      <c r="B144" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="C144" s="35"/>
-      <c r="D144" s="51" t="s">
+      <c r="C144" s="8"/>
+      <c r="D144" s="43" t="s">
         <v>439</v>
       </c>
-      <c r="E144" s="50"/>
-      <c r="F144" s="50"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A145" s="58" t="s">
+      <c r="E144" s="42"/>
+      <c r="F144" s="42"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="43" t="s">
         <v>436</v>
       </c>
-      <c r="B145" s="59" t="s">
+      <c r="B145" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="C145" s="35"/>
-      <c r="D145" s="51" t="s">
+      <c r="C145" s="8"/>
+      <c r="D145" s="43" t="s">
         <v>439</v>
       </c>
-      <c r="E145" s="50"/>
-      <c r="F145" s="50"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A146" s="58" t="s">
+      <c r="E145" s="42"/>
+      <c r="F145" s="42"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="43" t="s">
         <v>437</v>
       </c>
-      <c r="B146" s="59" t="s">
+      <c r="B146" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="C146" s="35"/>
-      <c r="D146" s="51" t="s">
+      <c r="C146" s="8"/>
+      <c r="D146" s="43" t="s">
         <v>439</v>
       </c>
-      <c r="E146" s="50"/>
-      <c r="F146" s="50"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A147" s="58" t="s">
+      <c r="E146" s="42"/>
+      <c r="F146" s="42"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="B147" s="53" t="s">
+      <c r="B147" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C147" s="35"/>
-      <c r="D147" s="51" t="s">
+      <c r="C147" s="8"/>
+      <c r="D147" s="43" t="s">
         <v>439</v>
       </c>
-      <c r="E147" s="50" t="s">
+      <c r="E147" s="42" t="s">
         <v>440</v>
       </c>
-      <c r="F147" s="50"/>
+      <c r="F147" s="42"/>
     </row>
     <row r="148" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A148" s="58" t="s">
+      <c r="A148" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="B148" s="60" t="s">
+      <c r="B148" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C148" s="35"/>
-      <c r="D148" s="51" t="s">
+      <c r="C148" s="8"/>
+      <c r="D148" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="E148" s="61" t="s">
+      <c r="E148" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="F148" s="50"/>
+      <c r="F148" s="42"/>
     </row>
     <row r="149" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A149" s="58" t="s">
+      <c r="A149" s="43" t="s">
         <v>446</v>
       </c>
-      <c r="B149" s="53" t="s">
+      <c r="B149" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C149" s="35" t="s">
+      <c r="C149" s="8" t="s">
         <v>450</v>
       </c>
-      <c r="D149" s="51" t="s">
+      <c r="D149" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="E149" s="61" t="s">
+      <c r="E149" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="F149" s="50" t="s">
+      <c r="F149" s="42" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A150" s="58" t="s">
+      <c r="A150" s="43" t="s">
         <v>447</v>
       </c>
-      <c r="B150" s="53" t="s">
+      <c r="B150" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C150" s="35"/>
-      <c r="D150" s="51" t="s">
+      <c r="C150" s="8"/>
+      <c r="D150" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="E150" s="61" t="s">
+      <c r="E150" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="F150" s="50" t="s">
+      <c r="F150" s="42" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A151" s="58" t="s">
+      <c r="A151" s="43" t="s">
         <v>448</v>
       </c>
-      <c r="B151" s="60" t="s">
+      <c r="B151" s="50" t="s">
         <v>171</v>
       </c>
-      <c r="C151" s="35" t="s">
+      <c r="C151" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="D151" s="51" t="s">
+      <c r="D151" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="E151" s="61" t="s">
+      <c r="E151" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="F151" s="50" t="s">
+      <c r="F151" s="42" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A152" s="58" t="s">
+      <c r="A152" s="43" t="s">
         <v>449</v>
       </c>
-      <c r="B152" s="60" t="s">
+      <c r="B152" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C152" s="35" t="s">
+      <c r="C152" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="D152" s="51" t="s">
+      <c r="D152" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="E152" s="61" t="s">
+      <c r="E152" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="F152" s="61" t="s">
+      <c r="F152" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A153" s="58" t="s">
+      <c r="A153" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="B153" s="40" t="s">
+      <c r="B153" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C153" s="35" t="s">
+      <c r="C153" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="D153" s="51"/>
-      <c r="E153" s="61" t="s">
+      <c r="D153" s="43"/>
+      <c r="E153" s="8" t="s">
         <v>463</v>
       </c>
-      <c r="F153" s="50" t="s">
+      <c r="F153" s="42" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A154" s="58" t="s">
+      <c r="A154" s="43" t="s">
         <v>460</v>
       </c>
-      <c r="B154" s="40" t="s">
+      <c r="B154" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C154" s="35" t="s">
+      <c r="C154" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="D154" s="51"/>
-      <c r="E154" s="61" t="s">
-        <v>280</v>
-      </c>
-      <c r="F154" s="57" t="s">
+      <c r="D154" s="43"/>
+      <c r="E154" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="F154" s="48" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A155" s="58" t="s">
+      <c r="A155" s="43" t="s">
         <v>465</v>
       </c>
-      <c r="B155" s="60" t="s">
+      <c r="B155" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="C155" s="35" t="s">
+      <c r="C155" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="D155" s="51"/>
-      <c r="E155" s="61" t="s">
+      <c r="D155" s="43"/>
+      <c r="E155" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="F155" s="50"/>
+      <c r="F155" s="42"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="50" t="s">
+      <c r="A156" s="42" t="s">
         <v>466</v>
       </c>
-      <c r="B156" s="52" t="s">
+      <c r="B156" s="44" t="s">
         <v>467</v>
       </c>
-      <c r="C156" s="40" t="s">
+      <c r="C156" s="26" t="s">
         <v>468</v>
       </c>
-      <c r="D156" s="51"/>
-      <c r="E156" s="50"/>
-      <c r="F156" s="35"/>
+      <c r="D156" s="43"/>
+      <c r="E156" s="42"/>
+      <c r="F156" s="8"/>
     </row>
     <row r="157" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A157" s="38" t="s">
+      <c r="A157" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="B157" s="38" t="s">
+      <c r="B157" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="C157" s="38" t="s">
+      <c r="C157" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="D157" s="35"/>
-      <c r="E157" s="35" t="s">
+      <c r="D157" s="8"/>
+      <c r="E157" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="F157" s="35" t="s">
+      <c r="F157" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A158" s="38" t="s">
+      <c r="A158" s="29" t="s">
         <v>476</v>
       </c>
-      <c r="B158" s="38" t="s">
+      <c r="B158" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="C158" s="38" t="s">
+      <c r="C158" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="D158" s="35"/>
-      <c r="E158" s="35" t="s">
+      <c r="D158" s="8"/>
+      <c r="E158" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="F158" s="35" t="s">
+      <c r="F158" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A159" s="38" t="s">
+      <c r="A159" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="B159" s="38" t="s">
+      <c r="B159" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C159" s="38" t="s">
+      <c r="C159" s="29" t="s">
         <v>485</v>
       </c>
-      <c r="D159" s="35"/>
-      <c r="E159" s="35" t="s">
+      <c r="D159" s="8"/>
+      <c r="E159" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="F159" s="35" t="s">
+      <c r="F159" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A160" s="38" t="s">
+      <c r="A160" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="B160" s="60" t="s">
+      <c r="B160" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="C160" s="38" t="s">
+      <c r="C160" s="29" t="s">
         <v>484</v>
       </c>
-      <c r="D160" s="35"/>
-      <c r="E160" s="35" t="s">
+      <c r="D160" s="8"/>
+      <c r="E160" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="F160" s="35" t="s">
+      <c r="F160" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A161" s="38" t="s">
+      <c r="A161" s="29" t="s">
         <v>486</v>
       </c>
-      <c r="B161" s="60" t="s">
+      <c r="B161" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="C161" s="38" t="s">
+      <c r="C161" s="29" t="s">
         <v>487</v>
       </c>
-      <c r="D161" s="35"/>
-      <c r="E161" s="35" t="s">
+      <c r="D161" s="8"/>
+      <c r="E161" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="F161" s="35" t="s">
+      <c r="F161" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A162" s="38" t="s">
+      <c r="A162" s="29" t="s">
         <v>498</v>
       </c>
-      <c r="B162" s="60" t="s">
+      <c r="B162" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C162" s="38"/>
-      <c r="D162" s="36"/>
-      <c r="E162" s="35" t="s">
+      <c r="C162" s="29"/>
+      <c r="D162" s="33"/>
+      <c r="E162" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="F162" s="35" t="s">
+      <c r="F162" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A163" s="38" t="s">
+      <c r="A163" s="29" t="s">
         <v>497</v>
       </c>
-      <c r="B163" s="60" t="s">
+      <c r="B163" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="C163" s="38" t="s">
+      <c r="C163" s="29" t="s">
         <v>496</v>
       </c>
-      <c r="D163" s="36"/>
-      <c r="E163" s="35" t="s">
+      <c r="D163" s="33"/>
+      <c r="E163" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="F163" s="35" t="s">
+      <c r="F163" s="8" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A164" s="58" t="s">
+      <c r="A164" s="43" t="s">
         <v>501</v>
       </c>
-      <c r="B164" s="53" t="s">
+      <c r="B164" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="C164" s="35" t="s">
+      <c r="C164" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="D164" s="54"/>
-      <c r="E164" s="61" t="s">
+      <c r="D164" s="51"/>
+      <c r="E164" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="F164" s="50" t="s">
+      <c r="F164" s="42" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A165" s="42" t="s">
+      <c r="A165" s="26" t="s">
         <v>505</v>
       </c>
-      <c r="B165" s="60" t="s">
+      <c r="B165" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C165" s="39" t="s">
+      <c r="C165" s="27" t="s">
         <v>506</v>
       </c>
-      <c r="D165" s="37" t="s">
+      <c r="D165" s="32" t="s">
         <v>507</v>
       </c>
-      <c r="E165" s="46" t="s">
+      <c r="E165" s="36" t="s">
         <v>508</v>
       </c>
-      <c r="F165" s="37" t="s">
+      <c r="F165" s="32" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A166" s="42" t="s">
+      <c r="A166" s="26" t="s">
         <v>509</v>
       </c>
-      <c r="B166" s="60" t="s">
+      <c r="B166" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="C166" s="39" t="s">
+      <c r="C166" s="27" t="s">
         <v>512</v>
       </c>
-      <c r="D166" s="37" t="s">
+      <c r="D166" s="32" t="s">
         <v>514</v>
       </c>
-      <c r="E166" s="46" t="s">
+      <c r="E166" s="36" t="s">
         <v>516</v>
       </c>
-      <c r="F166" s="37"/>
+      <c r="F166" s="32"/>
     </row>
     <row r="167" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A167" s="42" t="s">
+      <c r="A167" s="26" t="s">
         <v>510</v>
       </c>
-      <c r="B167" s="60" t="s">
+      <c r="B167" s="50" t="s">
         <v>511</v>
       </c>
-      <c r="C167" s="39" t="s">
+      <c r="C167" s="27" t="s">
         <v>513</v>
       </c>
-      <c r="D167" s="37" t="s">
+      <c r="D167" s="32" t="s">
         <v>515</v>
       </c>
-      <c r="E167" s="46" t="s">
+      <c r="E167" s="36" t="s">
         <v>517</v>
       </c>
-      <c r="F167" s="37"/>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A168" s="65" t="s">
+      <c r="F167" s="32"/>
+    </row>
+    <row r="168" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="10"/>
+      <c r="B168" s="10"/>
+      <c r="C168" s="10"/>
+      <c r="D168" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="B168" s="65"/>
-      <c r="C168" s="65"/>
-      <c r="D168" s="65"/>
-      <c r="E168" s="65"/>
-      <c r="F168" s="65"/>
+      <c r="E168" s="10"/>
+      <c r="F168" s="10"/>
     </row>
     <row r="169" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A169" s="40"/>
-      <c r="B169" s="40"/>
-      <c r="C169" s="62"/>
-      <c r="D169" s="35"/>
-      <c r="E169" s="63" t="s">
+      <c r="A169" s="26"/>
+      <c r="B169" s="26"/>
+      <c r="C169" s="52"/>
+      <c r="D169" s="8"/>
+      <c r="E169" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F169" s="35" t="s">
+      <c r="F169" s="8" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A170" s="40"/>
-      <c r="B170" s="40"/>
-      <c r="C170" s="39"/>
-      <c r="D170" s="35"/>
-      <c r="E170" s="63" t="s">
+      <c r="A170" s="26"/>
+      <c r="B170" s="26"/>
+      <c r="C170" s="27"/>
+      <c r="D170" s="8"/>
+      <c r="E170" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="F170" s="35" t="s">
+      <c r="F170" s="8" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="2480" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C2480" s="3"/>
-      <c r="D2480" s="3"/>
-      <c r="E2480" s="3" t="s">
+    <row r="2480" spans="5:5" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E2480" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F2480" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A72:G98">
     <sortCondition ref="C72:C98"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="A168:F168"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -6524,107 +6492,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="3" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
+      <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="12">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="12">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="5" t="s">
         <v>185</v>
       </c>
     </row>

--- a/references/Mapping_FCT_LOAN_template .xlsx
+++ b/references/Mapping_FCT_LOAN_template .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842B8FF3-69E8-024C-BFCA-8B799C8FF097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765B1760-C37C-ED4C-BE1F-F0367166E262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -111,12 +111,6 @@
   </si>
   <si>
     <t>Table description</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Bao gồm các trường màu đỏ</t>
   </si>
   <si>
     <t>FCT_LOAN</t>
@@ -2910,6 +2904,12 @@
   </si>
   <si>
     <t>Điều kiện lấy dữ liệu</t>
+  </si>
+  <si>
+    <t>Primary Key</t>
+  </si>
+  <si>
+    <t>DAYID + CONTRACT</t>
   </si>
 </sst>
 </file>
@@ -3126,7 +3126,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3199,9 +3199,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3614,116 +3611,116 @@
         <v>27</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>32</v>
+      <c r="B2" s="19" t="s">
+        <v>30</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="21" t="s">
-        <v>29</v>
+        <v>534</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>30</v>
+        <v>535</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="13"/>
       <c r="E5" s="18" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="13"/>
       <c r="E6" s="18" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13"/>
       <c r="E7" s="22" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="13"/>
       <c r="E8" s="22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
       <c r="E9" s="24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F9" s="22"/>
     </row>
     <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13"/>
       <c r="E10" s="24" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13"/>
       <c r="E11" s="24" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
@@ -3734,7 +3731,7 @@
     <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="13"/>
       <c r="E13" s="24" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F13" s="22"/>
     </row>
@@ -3745,22 +3742,22 @@
     </row>
     <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -3768,333 +3765,333 @@
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="D16" s="9" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="F17" s="29" t="s">
-        <v>170</v>
+      <c r="B17" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="26" t="s">
         <v>65</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>67</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A21" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A21" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>33</v>
+      <c r="C21" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A22" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>54</v>
+      <c r="A22" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>52</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A23" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>55</v>
+      <c r="A23" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>53</v>
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A24" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A25" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A24" s="29" t="s">
+      <c r="F25" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A26" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="8" t="s">
+      <c r="B26" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A25" s="29" t="s">
+      <c r="F26" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A27" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="D27" s="31"/>
+      <c r="E27" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A28" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A29" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A30" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="29" t="s">
+      <c r="B30" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A31" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A32" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A27" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>223</v>
-      </c>
-      <c r="D27" s="32"/>
-      <c r="E27" s="8" t="s">
+      <c r="B32" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A30" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A31" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="E31" s="8" t="s">
+      <c r="F32" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A33" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="32"/>
+      <c r="E33" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A32" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C32" s="32" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="33"/>
-      <c r="E33" s="8" t="s">
-        <v>308</v>
-      </c>
       <c r="F33" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="85" x14ac:dyDescent="0.2">
@@ -4102,2367 +4099,2367 @@
         <v>21</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>97</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>96</v>
+      <c r="A36" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>94</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="B37" s="34" t="s">
-        <v>198</v>
-      </c>
-      <c r="C37" s="27" t="s">
+      <c r="B37" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>5</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C38" s="27" t="s">
+      <c r="A38" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>1</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A39" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>215</v>
+      <c r="A39" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="26" t="s">
+        <v>213</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>216</v>
+      <c r="A40" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="26" t="s">
+        <v>214</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>217</v>
+      <c r="A41" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="26" t="s">
+        <v>215</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="34" t="s">
+      <c r="A42" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="C42" s="26" t="s">
+      <c r="B42" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C42" s="25" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A43" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C43" s="27" t="s">
+      <c r="A43" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C43" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="35" t="s">
-        <v>295</v>
+      <c r="D43" s="32"/>
+      <c r="E43" s="34" t="s">
+        <v>293</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="26" t="s">
+      <c r="A44" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="32"/>
+      <c r="E44" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A45" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="C44" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="33"/>
-      <c r="E44" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A45" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C45" s="27" t="s">
+      <c r="C45" s="26" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A46" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A46" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="27" t="s">
+      <c r="F46" s="8" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="26"/>
+      <c r="E47" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="32"/>
+      <c r="E48" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F48" s="8"/>
+    </row>
+    <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A49" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="26"/>
+      <c r="E49" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A50" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" s="32"/>
+      <c r="E50" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="F50" s="31" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A51" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D46" s="27"/>
-      <c r="E46" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C47" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C48" s="27" t="s">
+      <c r="D51" s="32"/>
+      <c r="E51" s="31" t="s">
+        <v>518</v>
+      </c>
+      <c r="F51" s="31" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A52" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C52" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="32"/>
+      <c r="E52" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A53" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C53" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="33"/>
-      <c r="E48" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F48" s="8"/>
-    </row>
-    <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="27"/>
-      <c r="E49" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A50" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C50" s="27" t="s">
+      <c r="D53" s="32"/>
+      <c r="E53" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A54" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D54" s="32"/>
+      <c r="E54" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A55" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C55" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="D55" s="32"/>
+      <c r="E55" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A56" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>492</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A57" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="E57" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D50" s="33"/>
-      <c r="E50" s="32" t="s">
-        <v>519</v>
-      </c>
-      <c r="F50" s="32" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A51" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C51" s="27" t="s">
+      <c r="F57" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A58" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A59" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D51" s="33"/>
-      <c r="E51" s="32" t="s">
-        <v>520</v>
-      </c>
-      <c r="F51" s="32" t="s">
+      <c r="F59" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A60" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>469</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A61" s="28" t="s">
+        <v>489</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>490</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A62" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="32"/>
+      <c r="E62" s="8" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A52" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="33"/>
-      <c r="E52" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="F52" s="32" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A53" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C53" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D53" s="33"/>
-      <c r="E53" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="F53" s="32" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A54" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D54" s="33"/>
-      <c r="E54" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="F54" s="32" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A55" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="B55" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C55" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D55" s="33"/>
-      <c r="E55" s="32" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" s="32" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A56" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="C56" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>494</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A57" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="C57" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="E57" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A58" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B58" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="C58" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D58" s="8"/>
-      <c r="E58" s="26" t="s">
-        <v>441</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A59" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" s="8"/>
-      <c r="E59" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A60" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B60" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C60" s="27" t="s">
-        <v>471</v>
-      </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A61" s="29" t="s">
-        <v>491</v>
-      </c>
-      <c r="B61" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>492</v>
-      </c>
-      <c r="D61" s="8"/>
-      <c r="E61" s="26" t="s">
-        <v>493</v>
-      </c>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A62" s="32" t="s">
+      <c r="F62" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A63" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="D63" s="32"/>
+      <c r="E63" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A64" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="B62" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="33"/>
-      <c r="E62" s="8" t="s">
+      <c r="B64" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="F62" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A63" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="B63" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C63" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="D63" s="33"/>
-      <c r="E63" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A64" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="B64" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>526</v>
-      </c>
-      <c r="E64" s="8" t="s">
-        <v>525</v>
-      </c>
       <c r="F64" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B65" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C65" s="27" t="s">
+      <c r="B65" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C65" s="26" t="s">
         <v>19</v>
       </c>
       <c r="D65" s="8"/>
-      <c r="E65" s="29" t="s">
-        <v>297</v>
+      <c r="E65" s="28" t="s">
+        <v>295</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="26" t="s">
-        <v>202</v>
+        <v>55</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="26" t="s">
-        <v>333</v>
-      </c>
-      <c r="B67" s="26" t="s">
-        <v>202</v>
+      <c r="A67" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A68" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="B68" s="26" t="s">
-        <v>202</v>
+      <c r="A68" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B68" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A69" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="B69" s="26" t="s">
-        <v>202</v>
+      <c r="A69" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D69" s="8"/>
       <c r="E69" s="8" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B70" s="26" t="s">
-        <v>202</v>
+        <v>56</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A71" s="26" t="s">
-        <v>321</v>
-      </c>
-      <c r="B71" s="26" t="s">
-        <v>202</v>
+      <c r="A71" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A72" s="26" t="s">
-        <v>322</v>
-      </c>
-      <c r="B72" s="26" t="s">
-        <v>202</v>
+      <c r="A72" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D72" s="8"/>
       <c r="E72" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="B73" s="26" t="s">
-        <v>202</v>
+        <v>228</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D73" s="8"/>
       <c r="E73" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="B74" s="26" t="s">
-        <v>202</v>
+        <v>233</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D74" s="35"/>
+        <v>232</v>
+      </c>
+      <c r="D74" s="34"/>
       <c r="E74" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A75" s="26" t="s">
-        <v>323</v>
-      </c>
-      <c r="B75" s="26" t="s">
-        <v>202</v>
+      <c r="A75" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A76" s="26" t="s">
-        <v>324</v>
-      </c>
-      <c r="B76" s="26" t="s">
-        <v>202</v>
+      <c r="A76" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D76" s="8"/>
       <c r="E76" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="26" t="s">
-        <v>202</v>
+        <v>61</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D77" s="8"/>
       <c r="E77" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B78" s="26" t="s">
-        <v>202</v>
+        <v>97</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B79" s="26" t="s">
-        <v>202</v>
+        <v>101</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B80" s="26" t="s">
-        <v>202</v>
+        <v>102</v>
+      </c>
+      <c r="B80" s="25" t="s">
+        <v>200</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D80" s="8"/>
       <c r="E80" s="8" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A81" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26" t="s">
-        <v>110</v>
+      <c r="A81" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25" t="s">
+        <v>108</v>
       </c>
       <c r="D81" s="8"/>
       <c r="E81" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A82" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B82" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C82" s="27"/>
+      <c r="A82" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C82" s="26"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A83" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="B83" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C83" s="26" t="s">
-        <v>143</v>
+      <c r="A83" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="B83" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="F83" s="37" t="s">
-        <v>139</v>
+        <v>127</v>
+      </c>
+      <c r="F83" s="36" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A84" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>198</v>
+      <c r="A84" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>196</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D84" s="8"/>
       <c r="E84" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="B85" s="26" t="s">
-        <v>204</v>
+      <c r="A85" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>202</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
       <c r="E85" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C86" s="27"/>
+      <c r="A86" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C86" s="26"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A87" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B87" s="26" t="s">
-        <v>206</v>
+      <c r="A87" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B87" s="25" t="s">
+        <v>204</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D87" s="8"/>
-      <c r="E87" s="37" t="s">
-        <v>131</v>
+      <c r="E87" s="36" t="s">
+        <v>129</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A88" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="B88" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="C88" s="27" t="s">
-        <v>211</v>
+      <c r="A88" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B88" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="C88" s="26" t="s">
+        <v>209</v>
       </c>
       <c r="D88" s="8"/>
       <c r="E88" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F88" s="8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B89" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C89" s="27"/>
+        <v>118</v>
+      </c>
+      <c r="B89" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" s="26"/>
       <c r="D89" s="8"/>
       <c r="E89" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A90" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="B90" s="26" t="s">
-        <v>203</v>
+      <c r="A90" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>201</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="B91" s="26" t="s">
-        <v>198</v>
+      <c r="A91" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>196</v>
       </c>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
       <c r="E91" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A92" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="B92" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="C92" s="26" t="s">
-        <v>147</v>
+      <c r="A92" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>145</v>
       </c>
       <c r="D92" s="8"/>
       <c r="E92" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A93" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="B93" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C93" s="26"/>
+      <c r="A93" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C93" s="25"/>
       <c r="D93" s="8"/>
       <c r="E93" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A94" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="B94" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="C94" s="26" t="s">
-        <v>148</v>
+      <c r="A94" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B94" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>146</v>
       </c>
       <c r="D94" s="8"/>
       <c r="E94" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="B95" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C95" s="26"/>
+      <c r="A95" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" s="25"/>
       <c r="D95" s="8"/>
       <c r="E95" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A96" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="B96" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="C96" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="D96" s="27"/>
-      <c r="E96" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="F96" s="27" t="s">
-        <v>280</v>
+      <c r="A96" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B96" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C96" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D96" s="26"/>
+      <c r="E96" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A97" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="B97" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="C97" s="27"/>
-      <c r="D97" s="27"/>
-      <c r="E97" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="F97" s="27" t="s">
-        <v>280</v>
+      <c r="A97" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="B97" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" s="38" t="s">
+      <c r="A98" s="37" t="s">
+        <v>316</v>
+      </c>
+      <c r="B98" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="C98" s="26"/>
+      <c r="D98" s="26"/>
+      <c r="E98" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="F98" s="26"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="26"/>
+      <c r="D99" s="26"/>
+      <c r="E99" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="B98" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="C98" s="27"/>
-      <c r="D98" s="27"/>
-      <c r="E98" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="F98" s="27"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="38" t="s">
-        <v>319</v>
-      </c>
-      <c r="B99" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C99" s="27"/>
-      <c r="D99" s="27"/>
-      <c r="E99" s="36" t="s">
-        <v>320</v>
-      </c>
-      <c r="F99" s="27"/>
+      <c r="F99" s="26"/>
     </row>
     <row r="100" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A100" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="B100" s="26" t="s">
+      <c r="A100" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="D100" s="31"/>
+      <c r="E100" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A101" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C101" s="26"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A102" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="25" t="s">
         <v>206</v>
-      </c>
-      <c r="C100" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="D100" s="32"/>
-      <c r="E100" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="F100" s="8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A101" s="29" t="s">
-        <v>257</v>
-      </c>
-      <c r="B101" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C101" s="27"/>
-      <c r="D101" s="40"/>
-      <c r="E101" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A102" s="29" t="s">
-        <v>224</v>
-      </c>
-      <c r="B102" s="26" t="s">
-        <v>208</v>
       </c>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
       <c r="E102" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A103" s="29" t="s">
-        <v>238</v>
-      </c>
-      <c r="B103" s="29" t="s">
-        <v>202</v>
+      <c r="A103" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B103" s="28" t="s">
+        <v>200</v>
       </c>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
       <c r="E103" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A104" s="29" t="s">
-        <v>239</v>
-      </c>
-      <c r="B104" s="29" t="s">
-        <v>243</v>
+      <c r="A104" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B104" s="28" t="s">
+        <v>241</v>
       </c>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
       <c r="E104" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="B105" s="29" t="s">
-        <v>243</v>
+      <c r="A105" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="B105" s="28" t="s">
+        <v>241</v>
       </c>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
       <c r="E105" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A106" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="B106" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C106" s="8"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A107" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C107" s="8"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="F107" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="F105" s="8" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="29" t="s">
+    </row>
+    <row r="108" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A108" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="B106" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C106" s="8"/>
-      <c r="D106" s="33"/>
-      <c r="E106" s="8" t="s">
+      <c r="B108" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C108" s="8"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F108" s="8" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="29" t="s">
+    <row r="109" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A109" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="B107" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C107" s="8"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="8" t="s">
+      <c r="B109" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C109" s="28"/>
+      <c r="D109" s="32"/>
+      <c r="E109" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A110" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C110" s="28"/>
+      <c r="D110" s="32"/>
+      <c r="E110" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A111" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>472</v>
+      </c>
+      <c r="D111" s="32"/>
+      <c r="E111" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F107" s="8" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A108" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="B108" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C108" s="8"/>
-      <c r="D108" s="33"/>
-      <c r="E108" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="F108" s="8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A109" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="B109" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="C109" s="29"/>
-      <c r="D109" s="33"/>
-      <c r="E109" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="F109" s="8" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A110" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="B110" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C110" s="29"/>
-      <c r="D110" s="33"/>
-      <c r="E110" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="F110" s="8" t="s">
+      <c r="F111" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A112" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="B112" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C112" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="D112" s="32"/>
+      <c r="E112" s="8" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A111" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="B111" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="C111" s="29" t="s">
-        <v>474</v>
-      </c>
-      <c r="D111" s="33"/>
-      <c r="E111" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="F111" s="8" t="s">
+      <c r="F112" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A113" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B113" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="C113" s="31"/>
+      <c r="D113" s="31"/>
+      <c r="E113" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="F113" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A114" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="B114" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C114" s="31"/>
+      <c r="D114" s="31"/>
+      <c r="E114" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="F114" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A115" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B115" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C115" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D115" s="31"/>
+      <c r="E115" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="F115" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A116" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="B116" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C116" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="D116" s="31"/>
+      <c r="E116" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="F116" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A117" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="B117" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="D117" s="31"/>
+      <c r="E117" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="F117" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A118" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="B118" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C118" s="26"/>
+      <c r="D118" s="31"/>
+      <c r="E118" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="F118" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A119" s="40" t="s">
+        <v>270</v>
+      </c>
+      <c r="B119" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C119" s="26"/>
+      <c r="D119" s="31"/>
+      <c r="E119" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="F119" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="68" x14ac:dyDescent="0.2">
+      <c r="A120" s="40" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="B112" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C112" s="29" t="s">
-        <v>242</v>
-      </c>
-      <c r="D112" s="33"/>
-      <c r="E112" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="F112" s="8" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="F113" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A114" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="B114" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C114" s="32"/>
-      <c r="D114" s="32"/>
-      <c r="E114" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="F114" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A115" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="B115" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="D115" s="32"/>
-      <c r="E115" s="36" t="s">
-        <v>442</v>
-      </c>
-      <c r="F115" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="B116" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C116" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="D116" s="32"/>
-      <c r="E116" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="F116" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="B117" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="D117" s="32"/>
-      <c r="E117" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="F117" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A118" s="41" t="s">
-        <v>273</v>
-      </c>
-      <c r="B118" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C118" s="27"/>
-      <c r="D118" s="32"/>
-      <c r="E118" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="F118" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A119" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="B119" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C119" s="27"/>
-      <c r="D119" s="32"/>
-      <c r="E119" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="F119" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A120" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="B120" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C120" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="D120" s="32"/>
-      <c r="E120" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="F120" s="32" t="s">
-        <v>280</v>
+      <c r="B120" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C120" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="D120" s="31"/>
+      <c r="E120" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="F120" s="31" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D121" s="31"/>
+      <c r="E121" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A122" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="B122" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C122" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="D122" s="31"/>
+      <c r="E122" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="153" x14ac:dyDescent="0.2">
+      <c r="A123" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B123" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="D123" s="31" t="s">
+        <v>335</v>
+      </c>
+      <c r="E123" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="F123" s="8"/>
+    </row>
+    <row r="124" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A124" s="41" t="s">
+        <v>338</v>
+      </c>
+      <c r="B124" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D121" s="32"/>
-      <c r="E121" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="F121" s="8" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A122" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="B122" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C122" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="D122" s="32"/>
-      <c r="E122" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="F122" s="8" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="153" x14ac:dyDescent="0.2">
-      <c r="A123" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="B123" s="26" t="s">
+      <c r="C124" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="D124" s="41"/>
+      <c r="E124" s="26" t="s">
+        <v>341</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A125" s="41" t="s">
+        <v>339</v>
+      </c>
+      <c r="B125" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C125" s="25"/>
+      <c r="D125" s="41"/>
+      <c r="E125" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="B126" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C126" s="25"/>
+      <c r="D126" s="41"/>
+      <c r="E126" s="41" t="s">
+        <v>377</v>
+      </c>
+      <c r="F126" s="8"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="B127" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C127" s="25"/>
+      <c r="D127" s="41"/>
+      <c r="E127" s="41" t="s">
+        <v>378</v>
+      </c>
+      <c r="F127" s="8"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="B128" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>462</v>
+      </c>
+      <c r="D128" s="41"/>
+      <c r="E128" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="F128" s="8"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="B129" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C129" s="25"/>
+      <c r="D129" s="41"/>
+      <c r="E129" s="41" t="s">
+        <v>379</v>
+      </c>
+      <c r="F129" s="8"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="B130" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" s="25"/>
+      <c r="D130" s="41"/>
+      <c r="E130" s="41" t="s">
+        <v>380</v>
+      </c>
+      <c r="F130" s="8"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="B131" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C131" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="D131" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E131" s="44" t="s">
+        <v>389</v>
+      </c>
+      <c r="F131" s="44"/>
+    </row>
+    <row r="132" spans="1:6" ht="60" x14ac:dyDescent="0.2">
+      <c r="A132" s="45" t="s">
+        <v>384</v>
+      </c>
+      <c r="B132" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="C123" s="26" t="s">
-        <v>339</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>337</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="F123" s="8"/>
-    </row>
-    <row r="124" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A124" s="42" t="s">
-        <v>340</v>
-      </c>
-      <c r="B124" s="43" t="s">
+      <c r="C132" s="44" t="s">
+        <v>388</v>
+      </c>
+      <c r="D132" s="42" t="s">
+        <v>386</v>
+      </c>
+      <c r="E132" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F132" s="44"/>
+    </row>
+    <row r="133" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A133" s="41" t="s">
+        <v>390</v>
+      </c>
+      <c r="B133" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="D133" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E133" s="41" t="s">
+        <v>396</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A134" s="41" t="s">
+        <v>427</v>
+      </c>
+      <c r="B134" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C134" s="8"/>
+      <c r="D134" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F134" s="8"/>
+    </row>
+    <row r="135" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A135" s="41" t="s">
+        <v>391</v>
+      </c>
+      <c r="B135" s="44" t="s">
+        <v>394</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D135" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E135" s="41" t="s">
+        <v>400</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A136" s="41" t="s">
+        <v>392</v>
+      </c>
+      <c r="B136" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="D136" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E136" s="41" t="s">
+        <v>403</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A137" s="41" t="s">
+        <v>393</v>
+      </c>
+      <c r="B137" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D137" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E137" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="45" x14ac:dyDescent="0.2">
+      <c r="A138" s="46" t="s">
+        <v>408</v>
+      </c>
+      <c r="B138" s="42" t="s">
+        <v>169</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D138" s="42" t="s">
+        <v>399</v>
+      </c>
+      <c r="E138" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="F138" s="47"/>
+    </row>
+    <row r="139" spans="1:6" ht="120" x14ac:dyDescent="0.2">
+      <c r="A139" s="42" t="s">
+        <v>414</v>
+      </c>
+      <c r="B139" s="44" t="s">
+        <v>416</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D139" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="E139" s="47" t="s">
+        <v>422</v>
+      </c>
+      <c r="F139" s="47" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="42" t="s">
+        <v>415</v>
+      </c>
+      <c r="B140" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C140" s="8"/>
+      <c r="D140" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="E140" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="F140" s="41" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="384" x14ac:dyDescent="0.2">
+      <c r="A141" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="B141" s="44" t="s">
+        <v>416</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="D141" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="E141" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="F141" s="47" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="B142" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C142" s="8"/>
+      <c r="D142" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="E142" s="41" t="s">
+        <v>420</v>
+      </c>
+      <c r="F142" s="41" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A143" s="42" t="s">
+        <v>428</v>
+      </c>
+      <c r="B143" s="48" t="s">
+        <v>202</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="D143" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="E143" s="41" t="s">
+        <v>431</v>
+      </c>
+      <c r="F143" s="41" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="B144" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C144" s="8"/>
+      <c r="D144" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="E144" s="41"/>
+      <c r="F144" s="41"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="B145" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C145" s="8"/>
+      <c r="D145" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="E145" s="41"/>
+      <c r="F145" s="41"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="42" t="s">
+        <v>435</v>
+      </c>
+      <c r="B146" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C146" s="8"/>
+      <c r="D146" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="E146" s="41"/>
+      <c r="F146" s="41"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="B147" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C147" s="8"/>
+      <c r="D147" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="E147" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="F147" s="41"/>
+    </row>
+    <row r="148" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A148" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="B148" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C148" s="8"/>
+      <c r="D148" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="F148" s="41"/>
+    </row>
+    <row r="149" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A149" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="B149" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="D149" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F149" s="41" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A150" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="B150" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C150" s="8"/>
+      <c r="D150" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="F150" s="41" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A151" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="B151" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="D151" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F151" s="41" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A152" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="B152" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="D152" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A153" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="B153" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="C124" s="26" t="s">
-        <v>342</v>
-      </c>
-      <c r="D124" s="42"/>
-      <c r="E124" s="27" t="s">
-        <v>343</v>
-      </c>
-      <c r="F124" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A125" s="42" t="s">
-        <v>341</v>
-      </c>
-      <c r="B125" s="44" t="s">
+      <c r="C153" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="D153" s="42"/>
+      <c r="E153" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="F153" s="41" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A154" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="D154" s="42"/>
+      <c r="E154" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="F154" s="47" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A155" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="B155" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="C125" s="26"/>
-      <c r="D125" s="42"/>
-      <c r="E125" s="42" t="s">
-        <v>344</v>
-      </c>
-      <c r="F125" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" s="42" t="s">
-        <v>374</v>
-      </c>
-      <c r="B126" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C126" s="26"/>
-      <c r="D126" s="42"/>
-      <c r="E126" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="F126" s="8"/>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" s="42" t="s">
-        <v>375</v>
-      </c>
-      <c r="B127" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C127" s="26"/>
-      <c r="D127" s="42"/>
-      <c r="E127" s="42" t="s">
-        <v>380</v>
-      </c>
-      <c r="F127" s="8"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="42" t="s">
-        <v>376</v>
-      </c>
-      <c r="B128" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="C128" s="26" t="s">
+      <c r="C155" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="D155" s="42"/>
+      <c r="E155" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="F155" s="41"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="41" t="s">
         <v>464</v>
       </c>
-      <c r="D128" s="42"/>
-      <c r="E128" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="F128" s="8"/>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" s="42" t="s">
-        <v>377</v>
-      </c>
-      <c r="B129" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="C129" s="26"/>
-      <c r="D129" s="42"/>
-      <c r="E129" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="F129" s="8"/>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="B130" s="44" t="s">
-        <v>171</v>
-      </c>
-      <c r="C130" s="26"/>
-      <c r="D130" s="42"/>
-      <c r="E130" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="F130" s="8"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" s="45" t="s">
-        <v>387</v>
-      </c>
-      <c r="B131" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C131" s="45" t="s">
-        <v>389</v>
-      </c>
-      <c r="D131" s="43" t="s">
-        <v>388</v>
-      </c>
-      <c r="E131" s="45" t="s">
-        <v>391</v>
-      </c>
-      <c r="F131" s="45"/>
-    </row>
-    <row r="132" spans="1:6" ht="60" x14ac:dyDescent="0.2">
-      <c r="A132" s="46" t="s">
-        <v>386</v>
-      </c>
-      <c r="B132" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="C132" s="45" t="s">
-        <v>390</v>
-      </c>
-      <c r="D132" s="43" t="s">
-        <v>388</v>
-      </c>
-      <c r="E132" s="45" t="s">
-        <v>413</v>
-      </c>
-      <c r="F132" s="45"/>
-    </row>
-    <row r="133" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A133" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="B133" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="D133" s="43" t="s">
-        <v>401</v>
-      </c>
-      <c r="E133" s="42" t="s">
-        <v>398</v>
-      </c>
-      <c r="F133" s="8" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A134" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="B134" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C134" s="8"/>
-      <c r="D134" s="43" t="s">
-        <v>401</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F134" s="8"/>
-    </row>
-    <row r="135" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A135" s="42" t="s">
-        <v>393</v>
-      </c>
-      <c r="B135" s="45" t="s">
-        <v>396</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>400</v>
-      </c>
-      <c r="D135" s="43" t="s">
-        <v>401</v>
-      </c>
-      <c r="E135" s="42" t="s">
-        <v>402</v>
-      </c>
-      <c r="F135" s="8" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A136" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="B136" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="D136" s="43" t="s">
-        <v>401</v>
-      </c>
-      <c r="E136" s="42" t="s">
-        <v>405</v>
-      </c>
-      <c r="F136" s="8" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A137" s="42" t="s">
-        <v>395</v>
-      </c>
-      <c r="B137" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="D137" s="43" t="s">
-        <v>401</v>
-      </c>
-      <c r="E137" s="42" t="s">
-        <v>408</v>
-      </c>
-      <c r="F137" s="8" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="45" x14ac:dyDescent="0.2">
-      <c r="A138" s="47" t="s">
-        <v>410</v>
-      </c>
-      <c r="B138" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="D138" s="43" t="s">
-        <v>401</v>
-      </c>
-      <c r="E138" s="48" t="s">
-        <v>412</v>
-      </c>
-      <c r="F138" s="48"/>
-    </row>
-    <row r="139" spans="1:6" ht="120" x14ac:dyDescent="0.2">
-      <c r="A139" s="43" t="s">
-        <v>416</v>
-      </c>
-      <c r="B139" s="45" t="s">
-        <v>418</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="D139" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="E139" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="F139" s="48" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="43" t="s">
-        <v>417</v>
-      </c>
-      <c r="B140" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C140" s="8"/>
-      <c r="D140" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="E140" s="42" t="s">
-        <v>422</v>
-      </c>
-      <c r="F140" s="42" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" ht="384" x14ac:dyDescent="0.2">
-      <c r="A141" s="43" t="s">
-        <v>414</v>
-      </c>
-      <c r="B141" s="45" t="s">
-        <v>418</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="D141" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="E141" s="48" t="s">
-        <v>423</v>
-      </c>
-      <c r="F141" s="48" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="43" t="s">
-        <v>415</v>
-      </c>
-      <c r="B142" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C142" s="8"/>
-      <c r="D142" s="43" t="s">
-        <v>421</v>
-      </c>
-      <c r="E142" s="42" t="s">
-        <v>422</v>
-      </c>
-      <c r="F142" s="42" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A143" s="43" t="s">
-        <v>430</v>
-      </c>
-      <c r="B143" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>431</v>
-      </c>
-      <c r="D143" s="43" t="s">
-        <v>432</v>
-      </c>
-      <c r="E143" s="42" t="s">
-        <v>433</v>
-      </c>
-      <c r="F143" s="42" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" s="43" t="s">
-        <v>435</v>
-      </c>
-      <c r="B144" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C144" s="8"/>
-      <c r="D144" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="E144" s="42"/>
-      <c r="F144" s="42"/>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="43" t="s">
-        <v>436</v>
-      </c>
-      <c r="B145" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C145" s="8"/>
-      <c r="D145" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="E145" s="42"/>
-      <c r="F145" s="42"/>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="43" t="s">
-        <v>437</v>
-      </c>
-      <c r="B146" s="49" t="s">
-        <v>171</v>
-      </c>
-      <c r="C146" s="8"/>
-      <c r="D146" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="E146" s="42"/>
-      <c r="F146" s="42"/>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="43" t="s">
-        <v>438</v>
-      </c>
-      <c r="B147" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C147" s="8"/>
-      <c r="D147" s="43" t="s">
-        <v>439</v>
-      </c>
-      <c r="E147" s="42" t="s">
-        <v>440</v>
-      </c>
-      <c r="F147" s="42"/>
-    </row>
-    <row r="148" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A148" s="43" t="s">
-        <v>443</v>
-      </c>
-      <c r="B148" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="C148" s="8"/>
-      <c r="D148" s="43" t="s">
-        <v>444</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="F148" s="42"/>
-    </row>
-    <row r="149" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A149" s="43" t="s">
-        <v>446</v>
-      </c>
-      <c r="B149" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="D149" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="F149" s="42" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A150" s="43" t="s">
-        <v>447</v>
-      </c>
-      <c r="B150" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C150" s="8"/>
-      <c r="D150" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="F150" s="42" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A151" s="43" t="s">
-        <v>448</v>
-      </c>
-      <c r="B151" s="50" t="s">
-        <v>171</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>490</v>
-      </c>
-      <c r="D151" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="E151" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="F151" s="42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A152" s="43" t="s">
-        <v>449</v>
-      </c>
-      <c r="B152" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="D152" s="43" t="s">
-        <v>452</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="F152" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A153" s="43" t="s">
-        <v>459</v>
-      </c>
-      <c r="B153" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="D153" s="43"/>
-      <c r="E153" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="F153" s="42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A154" s="43" t="s">
-        <v>460</v>
-      </c>
-      <c r="B154" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="D154" s="43"/>
-      <c r="E154" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="F154" s="48" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A155" s="43" t="s">
+      <c r="B156" s="43" t="s">
         <v>465</v>
       </c>
-      <c r="B155" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="D155" s="43"/>
-      <c r="E155" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="F155" s="42"/>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="42" t="s">
+      <c r="C156" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="B156" s="44" t="s">
-        <v>467</v>
-      </c>
-      <c r="C156" s="26" t="s">
-        <v>468</v>
-      </c>
-      <c r="D156" s="43"/>
-      <c r="E156" s="42"/>
+      <c r="D156" s="42"/>
+      <c r="E156" s="41"/>
       <c r="F156" s="8"/>
     </row>
     <row r="157" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A157" s="29" t="s">
-        <v>475</v>
-      </c>
-      <c r="B157" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="C157" s="29" t="s">
+      <c r="A157" s="28" t="s">
         <v>473</v>
+      </c>
+      <c r="B157" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C157" s="28" t="s">
+        <v>471</v>
       </c>
       <c r="D157" s="8"/>
       <c r="E157" s="8" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A158" s="29" t="s">
-        <v>476</v>
-      </c>
-      <c r="B158" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="C158" s="29" t="s">
-        <v>477</v>
+      <c r="A158" s="28" t="s">
+        <v>474</v>
+      </c>
+      <c r="B158" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="C158" s="28" t="s">
+        <v>475</v>
       </c>
       <c r="D158" s="8"/>
       <c r="E158" s="8" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A159" s="29" t="s">
-        <v>480</v>
-      </c>
-      <c r="B159" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="C159" s="29" t="s">
-        <v>485</v>
+      <c r="A159" s="28" t="s">
+        <v>478</v>
+      </c>
+      <c r="B159" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C159" s="28" t="s">
+        <v>483</v>
       </c>
       <c r="D159" s="8"/>
       <c r="E159" s="8" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="160" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A160" s="29" t="s">
+      <c r="A160" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="B160" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C160" s="28" t="s">
         <v>482</v>
-      </c>
-      <c r="B160" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="C160" s="29" t="s">
-        <v>484</v>
       </c>
       <c r="D160" s="8"/>
       <c r="E160" s="8" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A161" s="29" t="s">
-        <v>486</v>
-      </c>
-      <c r="B161" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="C161" s="29" t="s">
-        <v>487</v>
+      <c r="A161" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="B161" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="C161" s="28" t="s">
+        <v>485</v>
       </c>
       <c r="D161" s="8"/>
       <c r="E161" s="8" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A162" s="29" t="s">
+      <c r="A162" s="28" t="s">
+        <v>496</v>
+      </c>
+      <c r="B162" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C162" s="28"/>
+      <c r="D162" s="32"/>
+      <c r="E162" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="B162" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="C162" s="29"/>
-      <c r="D162" s="33"/>
-      <c r="E162" s="8" t="s">
+      <c r="F162" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A163" s="28" t="s">
+        <v>495</v>
+      </c>
+      <c r="B163" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="C163" s="28" t="s">
+        <v>494</v>
+      </c>
+      <c r="D163" s="32"/>
+      <c r="E163" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A164" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="B164" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D164" s="50"/>
+      <c r="E164" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="F162" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A163" s="29" t="s">
-        <v>497</v>
-      </c>
-      <c r="B163" s="50" t="s">
-        <v>243</v>
-      </c>
-      <c r="C163" s="29" t="s">
-        <v>496</v>
-      </c>
-      <c r="D163" s="33"/>
-      <c r="E163" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="F163" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A164" s="43" t="s">
+      <c r="F164" s="41" t="s">
         <v>501</v>
       </c>
-      <c r="B164" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="C164" s="8" t="s">
+    </row>
+    <row r="165" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A165" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="B165" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="C165" s="26" t="s">
         <v>504</v>
       </c>
-      <c r="D164" s="51"/>
-      <c r="E164" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="F164" s="42" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A165" s="26" t="s">
+      <c r="D165" s="31" t="s">
         <v>505</v>
       </c>
-      <c r="B165" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="C165" s="27" t="s">
+      <c r="E165" s="35" t="s">
         <v>506</v>
       </c>
-      <c r="D165" s="32" t="s">
+      <c r="F165" s="31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A166" s="25" t="s">
         <v>507</v>
       </c>
-      <c r="E165" s="36" t="s">
+      <c r="B166" s="49" t="s">
+        <v>509</v>
+      </c>
+      <c r="C166" s="26" t="s">
+        <v>510</v>
+      </c>
+      <c r="D166" s="31" t="s">
+        <v>512</v>
+      </c>
+      <c r="E166" s="35" t="s">
+        <v>514</v>
+      </c>
+      <c r="F166" s="31"/>
+    </row>
+    <row r="167" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A167" s="25" t="s">
         <v>508</v>
       </c>
-      <c r="F165" s="32" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A166" s="26" t="s">
+      <c r="B167" s="49" t="s">
         <v>509</v>
       </c>
-      <c r="B166" s="50" t="s">
+      <c r="C167" s="26" t="s">
         <v>511</v>
       </c>
-      <c r="C166" s="27" t="s">
-        <v>512</v>
-      </c>
-      <c r="D166" s="32" t="s">
-        <v>514</v>
-      </c>
-      <c r="E166" s="36" t="s">
-        <v>516</v>
-      </c>
-      <c r="F166" s="32"/>
-    </row>
-    <row r="167" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A167" s="26" t="s">
-        <v>510</v>
-      </c>
-      <c r="B167" s="50" t="s">
-        <v>511</v>
-      </c>
-      <c r="C167" s="27" t="s">
+      <c r="D167" s="31" t="s">
         <v>513</v>
       </c>
-      <c r="D167" s="32" t="s">
+      <c r="E167" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="E167" s="36" t="s">
-        <v>517</v>
-      </c>
-      <c r="F167" s="32"/>
+      <c r="F167" s="31"/>
     </row>
     <row r="168" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="10"/>
       <c r="D168" s="11" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
     </row>
     <row r="169" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A169" s="26"/>
-      <c r="B169" s="26"/>
-      <c r="C169" s="52"/>
+      <c r="A169" s="25"/>
+      <c r="B169" s="25"/>
+      <c r="C169" s="51"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A170" s="26"/>
-      <c r="B170" s="26"/>
-      <c r="C170" s="27"/>
+      <c r="A170" s="25"/>
+      <c r="B170" s="25"/>
+      <c r="C170" s="26"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2480" spans="5:5" s="19" customFormat="1" x14ac:dyDescent="0.2">
@@ -6493,24 +6490,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -6518,13 +6515,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="E3" s="5"/>
     </row>
@@ -6533,16 +6530,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -6550,16 +6547,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -6567,16 +6564,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -6584,16 +6581,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/references/Mapping_FCT_LOAN_template .xlsx
+++ b/references/Mapping_FCT_LOAN_template .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/references/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765B1760-C37C-ED4C-BE1F-F0367166E262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83D0E7A-81BE-BE49-BD53-79D113D45FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3600,9 +3600,9 @@
     <col min="1" max="1" width="34.33203125" style="19" customWidth="1"/>
     <col min="2" max="2" width="19" style="19" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="59.5" style="19" customWidth="1"/>
-    <col min="6" max="6" width="59.1640625" style="16" customWidth="1"/>
+    <col min="4" max="4" width="69.1640625" style="16" customWidth="1"/>
+    <col min="5" max="5" width="90.1640625" style="19" customWidth="1"/>
+    <col min="6" max="6" width="90.1640625" style="16" customWidth="1"/>
     <col min="7" max="16384" width="9.1640625" style="19"/>
   </cols>
   <sheetData>
